--- a/output/yearly_total_coral_cover_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_94_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254375541997231</v>
+        <v>1.25007548705263</v>
       </c>
       <c r="C3" t="n">
-        <v>4.622919257913727</v>
+        <v>4.593859525868021</v>
       </c>
       <c r="D3" t="n">
-        <v>6.068776611245244</v>
+        <v>6.084229320110089</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9460714111562</v>
+        <v>11.92816433303074</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.39066238021688</v>
+        <v>1.378707772903754</v>
       </c>
       <c r="C4" t="n">
-        <v>5.125574775497204</v>
+        <v>5.040139578583641</v>
       </c>
       <c r="D4" t="n">
-        <v>6.458305659106198</v>
+        <v>6.330767177168036</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97454281482028</v>
+        <v>12.74961452865543</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.576525807569898</v>
+        <v>1.566126356523539</v>
       </c>
       <c r="C5" t="n">
-        <v>5.780028557717893</v>
+        <v>5.591369400665658</v>
       </c>
       <c r="D5" t="n">
-        <v>6.783325514433805</v>
+        <v>6.619393222044121</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1398798797216</v>
+        <v>13.77688897923332</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.79185738300598</v>
+        <v>1.782779959375724</v>
       </c>
       <c r="C6" t="n">
-        <v>6.652721771245349</v>
+        <v>6.268127266715546</v>
       </c>
       <c r="D6" t="n">
-        <v>7.108346938379747</v>
+        <v>6.905977017058888</v>
       </c>
       <c r="E6" t="n">
-        <v>15.55292609263108</v>
+        <v>14.95688424315016</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.031788862242627</v>
+        <v>2.027641949731266</v>
       </c>
       <c r="C7" t="n">
-        <v>7.708504402496235</v>
+        <v>7.033454707956804</v>
       </c>
       <c r="D7" t="n">
-        <v>7.462517309704628</v>
+        <v>7.193000966892964</v>
       </c>
       <c r="E7" t="n">
-        <v>17.20281057444349</v>
+        <v>16.25409762458104</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.255549981502386</v>
+        <v>1.259970124116263</v>
       </c>
       <c r="C8" t="n">
-        <v>5.466205941299007</v>
+        <v>4.61103117066105</v>
       </c>
       <c r="D8" t="n">
-        <v>5.748786105915133</v>
+        <v>5.355849764174347</v>
       </c>
       <c r="E8" t="n">
-        <v>12.47054202871653</v>
+        <v>11.22685105895166</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.575392652807144</v>
+        <v>1.595109042858833</v>
       </c>
       <c r="C9" t="n">
-        <v>6.793995715634896</v>
+        <v>5.474659865738724</v>
       </c>
       <c r="D9" t="n">
-        <v>6.312548236711628</v>
+        <v>5.83691386143429</v>
       </c>
       <c r="E9" t="n">
-        <v>14.68193660515367</v>
+        <v>12.90668277003185</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.895806834448735</v>
+        <v>1.967206337434883</v>
       </c>
       <c r="C10" t="n">
-        <v>8.271650071694054</v>
+        <v>6.421711463066381</v>
       </c>
       <c r="D10" t="n">
-        <v>6.855875668128964</v>
+        <v>6.301485007005956</v>
       </c>
       <c r="E10" t="n">
-        <v>17.02333257427175</v>
+        <v>14.69040280750722</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.230547875602409</v>
+        <v>2.361555198086179</v>
       </c>
       <c r="C11" t="n">
-        <v>9.86364234196124</v>
+        <v>7.434524677716066</v>
       </c>
       <c r="D11" t="n">
-        <v>7.402787480656305</v>
+        <v>6.76981596595861</v>
       </c>
       <c r="E11" t="n">
-        <v>19.49697769821995</v>
+        <v>16.56589584176086</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.557272871017504</v>
+        <v>2.772737921853576</v>
       </c>
       <c r="C12" t="n">
-        <v>11.55032505768939</v>
+        <v>8.539301556978854</v>
       </c>
       <c r="D12" t="n">
-        <v>7.883443982179313</v>
+        <v>7.269657249405284</v>
       </c>
       <c r="E12" t="n">
-        <v>21.99104191088621</v>
+        <v>18.58169672823772</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.860559398740527</v>
+        <v>3.18023431318428</v>
       </c>
       <c r="C13" t="n">
-        <v>13.34996269836195</v>
+        <v>9.698990900161627</v>
       </c>
       <c r="D13" t="n">
-        <v>8.309026452972672</v>
+        <v>7.855788145938879</v>
       </c>
       <c r="E13" t="n">
-        <v>24.51954855007515</v>
+        <v>20.73501335928479</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.644879008557361</v>
+        <v>1.843074235090707</v>
       </c>
       <c r="C14" t="n">
-        <v>9.364763723608773</v>
+        <v>6.989385883275444</v>
       </c>
       <c r="D14" t="n">
-        <v>6.308867827122683</v>
+        <v>6.030827059802943</v>
       </c>
       <c r="E14" t="n">
-        <v>17.31851055928882</v>
+        <v>14.8632871781691</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.67498921064661</v>
+        <v>1.922468171933146</v>
       </c>
       <c r="C15" t="n">
-        <v>10.27745529433886</v>
+        <v>7.342805239327253</v>
       </c>
       <c r="D15" t="n">
-        <v>6.307503197813779</v>
+        <v>6.099461041806839</v>
       </c>
       <c r="E15" t="n">
-        <v>18.25994770279925</v>
+        <v>15.36473445306724</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.92534469270659</v>
+        <v>2.27129294872908</v>
       </c>
       <c r="C16" t="n">
-        <v>12.33433454446044</v>
+        <v>8.601287986447156</v>
       </c>
       <c r="D16" t="n">
-        <v>6.730567736004858</v>
+        <v>6.614554609794013</v>
       </c>
       <c r="E16" t="n">
-        <v>20.99024697317189</v>
+        <v>17.48713554497025</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.533588088803943</v>
+        <v>1.841621248488422</v>
       </c>
       <c r="C17" t="n">
-        <v>11.54807244308325</v>
+        <v>7.896147697871884</v>
       </c>
       <c r="D17" t="n">
-        <v>6.225075660565218</v>
+        <v>6.200875579655534</v>
       </c>
       <c r="E17" t="n">
-        <v>19.30673619245241</v>
+        <v>15.93864452601584</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.729378033461884</v>
+        <v>2.145855044557466</v>
       </c>
       <c r="C18" t="n">
-        <v>13.66485793811797</v>
+        <v>9.22215505208988</v>
       </c>
       <c r="D18" t="n">
-        <v>6.572938324610991</v>
+        <v>6.673145312783461</v>
       </c>
       <c r="E18" t="n">
-        <v>21.96717429619084</v>
+        <v>18.04115540943081</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.713130108956599</v>
+        <v>2.203041848329843</v>
       </c>
       <c r="C19" t="n">
-        <v>14.77689338019538</v>
+        <v>9.934422828997983</v>
       </c>
       <c r="D19" t="n">
-        <v>6.62544219183411</v>
+        <v>6.826170327444412</v>
       </c>
       <c r="E19" t="n">
-        <v>23.11546568098609</v>
+        <v>18.96363500477224</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.874009105251524</v>
+        <v>2.503014859362456</v>
       </c>
       <c r="C20" t="n">
-        <v>17.0060300825041</v>
+        <v>11.51263135095994</v>
       </c>
       <c r="D20" t="n">
-        <v>6.946630770755497</v>
+        <v>7.32306229299485</v>
       </c>
       <c r="E20" t="n">
-        <v>25.82666995851112</v>
+        <v>21.33870850331725</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.097211051743278</v>
+        <v>1.520854821079861</v>
       </c>
       <c r="C21" t="n">
-        <v>12.52779774705932</v>
+        <v>8.622739173784948</v>
       </c>
       <c r="D21" t="n">
-        <v>5.750449732947097</v>
+        <v>6.13069043627893</v>
       </c>
       <c r="E21" t="n">
-        <v>19.37545853174969</v>
+        <v>16.27428443114374</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_94_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25007548705263</v>
+        <v>1.270378029576454</v>
       </c>
       <c r="C3" t="n">
-        <v>4.593859525868021</v>
+        <v>4.588891882484533</v>
       </c>
       <c r="D3" t="n">
-        <v>6.084229320110089</v>
+        <v>6.130960510832237</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92816433303074</v>
+        <v>11.99023042289322</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378707772903754</v>
+        <v>1.418929129595568</v>
       </c>
       <c r="C4" t="n">
-        <v>5.040139578583641</v>
+        <v>4.993666716755581</v>
       </c>
       <c r="D4" t="n">
-        <v>6.330767177168036</v>
+        <v>6.50896294835079</v>
       </c>
       <c r="E4" t="n">
-        <v>12.74961452865543</v>
+        <v>12.92155879470194</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.566126356523539</v>
+        <v>1.614795692683576</v>
       </c>
       <c r="C5" t="n">
-        <v>5.591369400665658</v>
+        <v>5.477549857711169</v>
       </c>
       <c r="D5" t="n">
-        <v>6.619393222044121</v>
+        <v>6.899014950134279</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77688897923332</v>
+        <v>13.99136050052902</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.782779959375724</v>
+        <v>1.84152519923213</v>
       </c>
       <c r="C6" t="n">
-        <v>6.268127266715546</v>
+        <v>6.033101972149739</v>
       </c>
       <c r="D6" t="n">
-        <v>6.905977017058888</v>
+        <v>7.309880022476464</v>
       </c>
       <c r="E6" t="n">
-        <v>14.95688424315016</v>
+        <v>15.18450719385833</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.027641949731266</v>
+        <v>2.105595993701646</v>
       </c>
       <c r="C7" t="n">
-        <v>7.033454707956804</v>
+        <v>6.663712028777718</v>
       </c>
       <c r="D7" t="n">
-        <v>7.193000966892964</v>
+        <v>7.802817606475761</v>
       </c>
       <c r="E7" t="n">
-        <v>16.25409762458104</v>
+        <v>16.57212562895512</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.259970124116263</v>
+        <v>1.34777601358776</v>
       </c>
       <c r="C8" t="n">
-        <v>4.61103117066105</v>
+        <v>4.22250829819843</v>
       </c>
       <c r="D8" t="n">
-        <v>5.355849764174347</v>
+        <v>6.026971275900212</v>
       </c>
       <c r="E8" t="n">
-        <v>11.22685105895166</v>
+        <v>11.5972555876864</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.595109042858833</v>
+        <v>1.73657003718488</v>
       </c>
       <c r="C9" t="n">
-        <v>5.474659865738724</v>
+        <v>4.974103289063594</v>
       </c>
       <c r="D9" t="n">
-        <v>5.83691386143429</v>
+        <v>6.634619078972956</v>
       </c>
       <c r="E9" t="n">
-        <v>12.90668277003185</v>
+        <v>13.34529240522143</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.967206337434883</v>
+        <v>2.157379112451883</v>
       </c>
       <c r="C10" t="n">
-        <v>6.421711463066381</v>
+        <v>5.83945563800363</v>
       </c>
       <c r="D10" t="n">
-        <v>6.301485007005956</v>
+        <v>7.286578898151599</v>
       </c>
       <c r="E10" t="n">
-        <v>14.69040280750722</v>
+        <v>15.28341364860711</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.361555198086179</v>
+        <v>2.596432005543832</v>
       </c>
       <c r="C11" t="n">
-        <v>7.434524677716066</v>
+        <v>6.836035474500254</v>
       </c>
       <c r="D11" t="n">
-        <v>6.76981596595861</v>
+        <v>8.023494526227315</v>
       </c>
       <c r="E11" t="n">
-        <v>16.56589584176086</v>
+        <v>17.4559620062714</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.772737921853576</v>
+        <v>3.050047833445457</v>
       </c>
       <c r="C12" t="n">
-        <v>8.539301556978854</v>
+        <v>7.968328300095936</v>
       </c>
       <c r="D12" t="n">
-        <v>7.269657249405284</v>
+        <v>8.810541633726169</v>
       </c>
       <c r="E12" t="n">
-        <v>18.58169672823772</v>
+        <v>19.82891776726756</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.18023431318428</v>
+        <v>3.494424470585902</v>
       </c>
       <c r="C13" t="n">
-        <v>9.698990900161627</v>
+        <v>9.130422045586833</v>
       </c>
       <c r="D13" t="n">
-        <v>7.855788145938879</v>
+        <v>9.44114577065359</v>
       </c>
       <c r="E13" t="n">
-        <v>20.73501335928479</v>
+        <v>22.06599228682633</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.843074235090707</v>
+        <v>2.006024719041593</v>
       </c>
       <c r="C14" t="n">
-        <v>6.989385883275444</v>
+        <v>6.571455885577577</v>
       </c>
       <c r="D14" t="n">
-        <v>6.030827059802943</v>
+        <v>7.183516674313208</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8632871781691</v>
+        <v>15.76099727893238</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.922468171933146</v>
+        <v>2.093675154076748</v>
       </c>
       <c r="C15" t="n">
-        <v>7.342805239327253</v>
+        <v>7.00790164497754</v>
       </c>
       <c r="D15" t="n">
-        <v>6.099461041806839</v>
+        <v>7.34254998492415</v>
       </c>
       <c r="E15" t="n">
-        <v>15.36473445306724</v>
+        <v>16.44412678397844</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.27129294872908</v>
+        <v>2.482663229453419</v>
       </c>
       <c r="C16" t="n">
-        <v>8.601287986447156</v>
+        <v>8.250568436582023</v>
       </c>
       <c r="D16" t="n">
-        <v>6.614554609794013</v>
+        <v>8.009245033401116</v>
       </c>
       <c r="E16" t="n">
-        <v>17.48713554497025</v>
+        <v>18.74247669943656</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.841621248488422</v>
+        <v>2.026150546978652</v>
       </c>
       <c r="C17" t="n">
-        <v>7.896147697871884</v>
+        <v>7.666084940858686</v>
       </c>
       <c r="D17" t="n">
-        <v>6.200875579655534</v>
+        <v>7.571964788452545</v>
       </c>
       <c r="E17" t="n">
-        <v>15.93864452601584</v>
+        <v>17.26420027628988</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.145855044557466</v>
+        <v>2.35466296377372</v>
       </c>
       <c r="C18" t="n">
-        <v>9.22215505208988</v>
+        <v>8.905227258204926</v>
       </c>
       <c r="D18" t="n">
-        <v>6.673145312783461</v>
+        <v>8.170389101576188</v>
       </c>
       <c r="E18" t="n">
-        <v>18.04115540943081</v>
+        <v>19.43027932355484</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.203041848329843</v>
+        <v>2.404035055820292</v>
       </c>
       <c r="C19" t="n">
-        <v>9.934422828997983</v>
+        <v>9.49255782227058</v>
       </c>
       <c r="D19" t="n">
-        <v>6.826170327444412</v>
+        <v>8.382534962986881</v>
       </c>
       <c r="E19" t="n">
-        <v>18.96363500477224</v>
+        <v>20.27912784107775</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.503014859362456</v>
+        <v>2.719735665074939</v>
       </c>
       <c r="C20" t="n">
-        <v>11.51263135095994</v>
+        <v>10.91633743035452</v>
       </c>
       <c r="D20" t="n">
-        <v>7.32306229299485</v>
+        <v>8.975490941397871</v>
       </c>
       <c r="E20" t="n">
-        <v>21.33870850331725</v>
+        <v>22.61156403682732</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.520854821079861</v>
+        <v>1.640038992375424</v>
       </c>
       <c r="C21" t="n">
-        <v>8.622739173784948</v>
+        <v>8.063614221262304</v>
       </c>
       <c r="D21" t="n">
-        <v>6.13069043627893</v>
+        <v>7.550199441849393</v>
       </c>
       <c r="E21" t="n">
-        <v>16.27428443114374</v>
+        <v>17.25385265548712</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_94_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270378029576454</v>
+        <v>2.60386932290326</v>
       </c>
       <c r="C3" t="n">
-        <v>4.588891882484533</v>
+        <v>7.842188013402986</v>
       </c>
       <c r="D3" t="n">
-        <v>6.130960510832237</v>
+        <v>8.140207982205062</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99023042289322</v>
+        <v>18.58626531851131</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.418929129595568</v>
+        <v>1.104211233732709</v>
       </c>
       <c r="C4" t="n">
-        <v>4.993666716755581</v>
+        <v>4.797045422996798</v>
       </c>
       <c r="D4" t="n">
-        <v>6.50896294835079</v>
+        <v>5.656446757157539</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92155879470194</v>
+        <v>11.55770341388705</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.614795692683576</v>
+        <v>1.233387780373211</v>
       </c>
       <c r="C5" t="n">
-        <v>5.477549857711169</v>
+        <v>5.739764845019672</v>
       </c>
       <c r="D5" t="n">
-        <v>6.899014950134279</v>
+        <v>5.905729703902079</v>
       </c>
       <c r="E5" t="n">
-        <v>13.99136050052902</v>
+        <v>12.87888232929496</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.84152519923213</v>
+        <v>1.384988157945976</v>
       </c>
       <c r="C6" t="n">
-        <v>6.033101972149739</v>
+        <v>6.892834239331853</v>
       </c>
       <c r="D6" t="n">
-        <v>7.309880022476464</v>
+        <v>6.195231733545094</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18450719385833</v>
+        <v>14.47305413082292</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.105595993701646</v>
+        <v>1.540944119329918</v>
       </c>
       <c r="C7" t="n">
-        <v>6.663712028777718</v>
+        <v>8.191687453986185</v>
       </c>
       <c r="D7" t="n">
-        <v>7.802817606475761</v>
+        <v>6.444810491909087</v>
       </c>
       <c r="E7" t="n">
-        <v>16.57212562895512</v>
+        <v>16.17744206522519</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.34777601358776</v>
+        <v>1.691819053296749</v>
       </c>
       <c r="C8" t="n">
-        <v>4.22250829819843</v>
+        <v>9.62427540401946</v>
       </c>
       <c r="D8" t="n">
-        <v>6.026971275900212</v>
+        <v>6.688880945863115</v>
       </c>
       <c r="E8" t="n">
-        <v>11.5972555876864</v>
+        <v>18.00497540317932</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.73657003718488</v>
+        <v>1.835006775173405</v>
       </c>
       <c r="C9" t="n">
-        <v>4.974103289063594</v>
+        <v>11.20452039028729</v>
       </c>
       <c r="D9" t="n">
-        <v>6.634619078972956</v>
+        <v>6.989735155573934</v>
       </c>
       <c r="E9" t="n">
-        <v>13.34529240522143</v>
+        <v>20.02926232103463</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.157379112451883</v>
+        <v>1.123021198887926</v>
       </c>
       <c r="C10" t="n">
-        <v>5.83945563800363</v>
+        <v>8.022881509013104</v>
       </c>
       <c r="D10" t="n">
-        <v>7.286578898151599</v>
+        <v>5.47719007694704</v>
       </c>
       <c r="E10" t="n">
-        <v>15.28341364860711</v>
+        <v>14.62309278484807</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.596432005543832</v>
+        <v>1.066875047682051</v>
       </c>
       <c r="C11" t="n">
-        <v>6.836035474500254</v>
+        <v>8.7028988738367</v>
       </c>
       <c r="D11" t="n">
-        <v>8.023494526227315</v>
+        <v>5.230388521576434</v>
       </c>
       <c r="E11" t="n">
-        <v>17.4559620062714</v>
+        <v>15.00016244309518</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.050047833445457</v>
+        <v>1.165363977372091</v>
       </c>
       <c r="C12" t="n">
-        <v>7.968328300095936</v>
+        <v>10.38596786808926</v>
       </c>
       <c r="D12" t="n">
-        <v>8.810541633726169</v>
+        <v>5.493094389755838</v>
       </c>
       <c r="E12" t="n">
-        <v>19.82891776726756</v>
+        <v>17.04442623521719</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.494424470585902</v>
+        <v>0.9286449709241006</v>
       </c>
       <c r="C13" t="n">
-        <v>9.130422045586833</v>
+        <v>9.904175182230141</v>
       </c>
       <c r="D13" t="n">
-        <v>9.44114577065359</v>
+        <v>4.904615180876215</v>
       </c>
       <c r="E13" t="n">
-        <v>22.06599228682633</v>
+        <v>15.73743533403046</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.006024719041593</v>
+        <v>1.014017751285403</v>
       </c>
       <c r="C14" t="n">
-        <v>6.571455885577577</v>
+        <v>11.66249513801322</v>
       </c>
       <c r="D14" t="n">
-        <v>7.183516674313208</v>
+        <v>5.147322848320111</v>
       </c>
       <c r="E14" t="n">
-        <v>15.76099727893238</v>
+        <v>17.82383573761874</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.093675154076748</v>
+        <v>0.9903674490900974</v>
       </c>
       <c r="C15" t="n">
-        <v>7.00790164497754</v>
+        <v>12.61010747458337</v>
       </c>
       <c r="D15" t="n">
-        <v>7.34254998492415</v>
+        <v>5.103556535664789</v>
       </c>
       <c r="E15" t="n">
-        <v>16.44412678397844</v>
+        <v>18.70403145933826</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.482663229453419</v>
+        <v>1.081022032100248</v>
       </c>
       <c r="C16" t="n">
-        <v>8.250568436582023</v>
+        <v>14.67683365417854</v>
       </c>
       <c r="D16" t="n">
-        <v>8.009245033401116</v>
+        <v>5.460127301847231</v>
       </c>
       <c r="E16" t="n">
-        <v>18.74247669943656</v>
+        <v>21.21798298812602</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.026150546978652</v>
+        <v>0.6433000006847651</v>
       </c>
       <c r="C17" t="n">
-        <v>7.666084940858686</v>
+        <v>10.89756641424932</v>
       </c>
       <c r="D17" t="n">
-        <v>7.571964788452545</v>
+        <v>4.487981090147954</v>
       </c>
       <c r="E17" t="n">
-        <v>17.26420027628988</v>
+        <v>16.02884750508204</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.35466296377372</v>
+        <v>0.5139547406502478</v>
       </c>
       <c r="C18" t="n">
-        <v>8.905227258204926</v>
+        <v>9.768713633998164</v>
       </c>
       <c r="D18" t="n">
-        <v>8.170389101576188</v>
+        <v>4.008073359880986</v>
       </c>
       <c r="E18" t="n">
-        <v>19.43027932355484</v>
+        <v>14.2907417345294</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.404035055820292</v>
+        <v>0.6018211601803372</v>
       </c>
       <c r="C19" t="n">
-        <v>9.49255782227058</v>
+        <v>12.08042513571109</v>
       </c>
       <c r="D19" t="n">
-        <v>8.382534962986881</v>
+        <v>4.375384445947887</v>
       </c>
       <c r="E19" t="n">
-        <v>20.27912784107775</v>
+        <v>17.05763074183931</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.719735665074939</v>
+        <v>0.6871055832482577</v>
       </c>
       <c r="C20" t="n">
-        <v>10.91633743035452</v>
+        <v>14.59531914229493</v>
       </c>
       <c r="D20" t="n">
-        <v>8.975490941397871</v>
+        <v>4.749096527046478</v>
       </c>
       <c r="E20" t="n">
-        <v>22.61156403682732</v>
+        <v>20.03152125258966</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.640038992375424</v>
+        <v>0.7620718379445441</v>
       </c>
       <c r="C21" t="n">
-        <v>8.063614221262304</v>
+        <v>17.13075131085161</v>
       </c>
       <c r="D21" t="n">
-        <v>7.550199441849393</v>
+        <v>5.060506898833567</v>
       </c>
       <c r="E21" t="n">
-        <v>17.25385265548712</v>
+        <v>22.95333004762973</v>
       </c>
     </row>
   </sheetData>
